--- a/data/fokito/misiones.xlsx
+++ b/data/fokito/misiones.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Plan" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Misiones'!$A$1:$H$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matriz'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Misiones'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matriz'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan'!$A$1:$H$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,16 +468,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="51" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -525,24 +525,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46134</v>
+        <v>46150</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46148</v>
+        <v>46136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Trabajo práctico</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>revisar_tp</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cada profesor: 2 alternativas + 1 desarrollo (según tema de la prueba).</t>
+          <t>Revisar TP y poner nota. — Entrega al final</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -563,34 +563,34 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46141</v>
+        <v>46195</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46148</v>
+        <v>46216</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>construir_control</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Armar versión final, diagramación y revisión cruzada.</t>
+          <t>Preguntas examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -601,34 +601,34 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46148</v>
+        <v>46216</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pauta_prueba</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pauta oficial: dividir en 2 mitades si son 2 responsables.</t>
+          <t>Preguntas examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -639,34 +639,34 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46145</v>
+        <v>46197</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46148</v>
+        <v>46218</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>revisar_prueba</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Revisión final (errores, coherencia, puntajes).</t>
+          <t>Preguntas examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,19 +677,19 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46150</v>
+        <v>46197</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46148</v>
+        <v>46218</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>escanear</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -699,12 +699,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Escanear pruebas/controles y subir a carpeta.</t>
+          <t>Preguntas examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -715,34 +715,34 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46150</v>
+        <v>46202</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46136</v>
+        <v>46216</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Trabajo práctico</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>revisar_tp</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p6, p1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Revisar TP y poner nota; subir rúbrica si aplica.</t>
+          <t>Construcción examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -753,34 +753,34 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46162</v>
+        <v>46202</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46148</v>
+        <v>46223</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>corregir_y_notas</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corrección por sección. Subir nota final.</t>
+          <t>Preguntas examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -791,10 +791,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -803,22 +803,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p4, p5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Preguntas para examen (temas por unidad).</t>
+          <t>Construcción examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -829,10 +829,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46189</v>
+        <v>46202</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Preguntas para examen (temas por unidad).</t>
+          <t>Preguntas examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -867,10 +867,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46190</v>
+        <v>46204</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p6, p1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Preguntas para examen (temas por unidad).</t>
+          <t>Construcción examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -905,10 +905,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46191</v>
+        <v>46204</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Preguntas para examen (temas por unidad).</t>
+          <t>Preguntas examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -943,10 +943,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46195</v>
+        <v>46204</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>46209</v>
+        <v>46218</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -960,17 +960,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Construcción examen final + revisión cruzada.</t>
+          <t>Construcción examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -981,10 +981,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46196</v>
+        <v>46204</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -993,22 +993,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Construcción examen final + revisión cruzada.</t>
+          <t>Preguntas examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1019,10 +1019,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46197</v>
+        <v>46209</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1031,22 +1031,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>pauta_examen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sección 3</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>p6, p5</t>
+          <t>p2, p5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Construcción examen final + revisión cruzada.</t>
+          <t>Pauta examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1057,10 +1057,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46198</v>
+        <v>46209</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46212</v>
+        <v>46223</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>p3, p2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Construcción examen final + revisión cruzada.</t>
+          <t>Construcción examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1095,10 +1095,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46202</v>
+        <v>46209</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1112,17 +1112,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>p6, p4</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pauta oficial examen.</t>
+          <t>Pauta examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p4, p5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pauta oficial examen.</t>
+          <t>Construcción examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1171,10 +1171,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pauta oficial examen.</t>
+          <t>Pauta examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1209,10 +1209,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1221,22 +1221,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>p3, p6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pauta oficial examen.</t>
+          <t>Construcción examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1247,10 +1247,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46223</v>
+        <v>46211</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46209</v>
+        <v>46218</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1259,22 +1259,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>pauta_examen</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Corrección examen por sección.</t>
+          <t>Pauta examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1285,10 +1285,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46224</v>
+        <v>46211</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 4</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p5, p3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Corrección examen por sección.</t>
+          <t>Construcción examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1323,10 +1323,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46225</v>
+        <v>46216</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1335,22 +1335,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>pauta_examen</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sección 3</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Corrección examen por sección.</t>
+          <t>Pauta examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46226</v>
+        <v>46216</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>46212</v>
+        <v>46223</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1373,32 +1373,412 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>p6, p5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pauta examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sección 3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pauta examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sección 4</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pauta examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>corregir_examen</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sección 3</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>Sección 4</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>p6</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Corrección examen por sección.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sección 3</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sección 4</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H24"/>
+  <autoFilter ref="A1:H34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1409,40 +1789,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Evaluaciones</t>
+          <t>Evaluación</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Sección 1 (lunes - DA)</t>
+          <t>Misión</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Sección 2 (viernes - JL)</t>
+          <t>Detalle</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Sección 3 (martes - JL)</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>Sección 4 (miércoles - ??)</t>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Sección 3</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Sección 4</t>
         </is>
       </c>
     </row>
@@ -1454,57 +1846,321 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>Construcción examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p6, p1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p4, p5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>p6, p1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>p2, p4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prueba</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>construir_examen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Construcción examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>p3, p2</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4, p5</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>p3, p6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>p5, p3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pauta examen. — Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>p2, p5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>p1, p2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>p4, p3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>p1, p3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pauta examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>p3, p1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>p6, p5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Preguntas examen. — Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Preguntas examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Trabajo práctico</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>revisar_tp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Revisar TP y poner nota. — Entrega al final</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1515,16 +2171,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="51" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1572,10 +2228,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1599,7 +2255,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Preguntas para examen (temas por unidad).</t>
+          <t>Preguntas examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1610,10 +2266,10 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46189</v>
+        <v>46202</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1627,7 +2283,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1637,7 +2293,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Preguntas para examen (temas por unidad).</t>
+          <t>Preguntas examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1648,10 +2304,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1665,7 +2321,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sección 3</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1675,7 +2331,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Preguntas para examen (temas por unidad).</t>
+          <t>Preguntas examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1686,10 +2342,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46212</v>
+        <v>46223</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1703,7 +2359,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1713,7 +2369,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Preguntas para examen (temas por unidad).</t>
+          <t>Preguntas examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1724,10 +2380,10 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46209</v>
+        <v>46218</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1736,22 +2392,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Construcción examen final + revisión cruzada.</t>
+          <t>Preguntas examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1762,10 +2418,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46196</v>
+        <v>46204</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1774,22 +2430,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Construcción examen final + revisión cruzada.</t>
+          <t>Preguntas examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1803,7 +2459,7 @@
         <v>46197</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1812,22 +2468,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sección 3</t>
+          <t>Sección 4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>p6, p5</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Construcción examen final + revisión cruzada.</t>
+          <t>Preguntas examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1838,10 +2494,10 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46198</v>
+        <v>46204</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1850,7 +2506,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>construir_examen</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1860,12 +2516,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Construcción examen final + revisión cruzada.</t>
+          <t>Preguntas examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1879,7 +2535,7 @@
         <v>46202</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1888,7 +2544,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1898,12 +2554,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p6, p4</t>
+          <t>p6, p1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pauta oficial examen.</t>
+          <t>Construcción examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1914,10 +2570,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1926,22 +2582,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p3, p2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pauta oficial examen.</t>
+          <t>Construcción examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1952,10 +2608,10 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46204</v>
+        <v>46202</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1964,22 +2620,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sección 3</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p4, p5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pauta oficial examen.</t>
+          <t>Construcción examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1990,10 +2646,10 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>46212</v>
+        <v>46223</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,22 +2658,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>p4, p5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pauta oficial examen.</t>
+          <t>Construcción examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2028,10 +2684,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46223</v>
+        <v>46204</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46209</v>
+        <v>46218</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,22 +2696,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p6, p1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corrección examen por sección.</t>
+          <t>Construcción examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2066,10 +2722,10 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46224</v>
+        <v>46211</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,22 +2734,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3, p6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corrección examen por sección.</t>
+          <t>Construcción examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2104,10 +2760,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46225</v>
+        <v>46204</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2116,22 +2772,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sección 3</t>
+          <t>Sección 4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corrección examen por sección.</t>
+          <t>Construcción examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2142,10 +2798,10 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46226</v>
+        <v>46211</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2154,7 +2810,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2164,12 +2820,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p5, p3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corrección examen por sección.</t>
+          <t>Construcción examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2180,34 +2836,34 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46134</v>
+        <v>46209</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46148</v>
+        <v>46216</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>pauta_examen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p2, p5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cada profesor: 2 alternativas + 1 desarrollo (según tema de la prueba).</t>
+          <t>Pauta examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2218,34 +2874,34 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46141</v>
+        <v>46216</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46148</v>
+        <v>46223</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>construir_control</t>
+          <t>pauta_examen</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Armar versión final, diagramación y revisión cruzada.</t>
+          <t>Pauta examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2256,34 +2912,34 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46143</v>
+        <v>46209</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46148</v>
+        <v>46216</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>pauta_prueba</t>
+          <t>pauta_examen</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pauta oficial: dividir en 2 mitades si son 2 responsables.</t>
+          <t>Pauta examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2294,34 +2950,34 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46145</v>
+        <v>46216</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46148</v>
+        <v>46223</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>revisar_prueba</t>
+          <t>pauta_examen</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p6, p5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Revisión final (errores, coherencia, puntajes).</t>
+          <t>Pauta examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2332,34 +2988,34 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46162</v>
+        <v>46211</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46148</v>
+        <v>46218</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>corregir_y_notas</t>
+          <t>pauta_examen</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Corrección por sección. Subir nota final.</t>
+          <t>Pauta examen. — Examen Primera Oportunidad</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2370,34 +3026,34 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46150</v>
+        <v>46218</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46148</v>
+        <v>46225</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>escanear</t>
+          <t>pauta_examen</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sección 4</t>
+          <t>Sección 3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4, p5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Escanear pruebas/controles y subir a carpeta.</t>
+          <t>Pauta examen. — Examen Segunda Oportunidad</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2408,44 +3064,424 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sección 4</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>p1, p3</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pauta examen. — Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sección 4</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>p4, p5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pauta examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sección 3</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sección 3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sección 4</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>corregir_examen</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sección 4</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Corrección examen. — Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
         <v>46150</v>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B34" s="3" t="n">
         <v>46136</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Trabajo práctico</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>revisar_tp</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Sección 2</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Revisar TP y poner nota; subir rúbrica si aplica.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Revisar TP y poner nota. — Entrega al final</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H24"/>
+  <autoFilter ref="A1:H34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/fokito/misiones.xlsx
+++ b/data/fokito/misiones.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>p5, p3</t>
+          <t>p3, p2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>p6, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1893,22 +1893,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>p1, p3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>p4, p3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>p4, p3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>p3, p2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>p4, p5</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>p3, p6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>p5, p3</t>
         </is>
       </c>
     </row>
@@ -1930,22 +1930,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>p4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>p6</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>p1, p2</t>
         </is>
       </c>
     </row>
@@ -2041,22 +2041,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>p6, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p3, p4</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>p5, p3</t>
+          <t>p3, p2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>p6, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">

--- a/data/fokito/misiones.xlsx
+++ b/data/fokito/misiones.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 1||JM, MB, NV</t>
+          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 3||EG, RM, XX</t>
+          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 4||SM, XX, XX</t>
+          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 1||JM, MB, NV</t>
+          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 3||EG, RM, XX</t>
+          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 4||SM, XX, XX</t>
+          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-05-08||2026-05-01||Día Nacional del Trabajo||Laboratorio||corregir_informe_laboratorio||Sección 3||EG, AR, XX, XX</t>
+          <t>2026-05-08||2026-05-01||Día Nacional del Trabajo||Laboratorio||corregir_informe_laboratorio||Sección 3||AR, JM, MB, EG</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-06-10||2026-06-03||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||JM, MB, NV</t>
+          <t>2026-06-10||2026-06-03||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 3||EG, RM, XX</t>
+          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 4||SM, XX, XX</t>
+          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 1||JM, MB, NV</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||EG, RM, XX</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||EG, RM, XX</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||SM, XX, XX</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||SM, XX, XX</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-06-29||2026-07-13||Examen 1||Examen||pedir_preguntas||Sección 1||JM, MB, NV</t>
+          <t>2026-06-29||2026-07-13||Examen 1||Examen||pedir_preguntas||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 3||EG, RM, XX</t>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 4||SM, XX, XX</t>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-03||2026-06-26||Avance Laboratorio 2||Laboratorio||corregir_informe_laboratorio||Sección 3||EG, AR, XX, XX</t>
+          <t>2026-07-03||2026-06-26||Avance Laboratorio 2||Laboratorio||corregir_informe_laboratorio||Sección 3||AR, JM, MB, EG</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-06||2026-07-20||Examen 2||Examen||pedir_preguntas||Sección 1||JM, MB, NV</t>
+          <t>2026-07-06||2026-07-20||Examen 2||Examen||pedir_preguntas||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 3||EG, RM, XX</t>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 4||SM, XX, XX</t>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 1||JM, MB, NV</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||EG, RM, XX</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||EG, RM, XX</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||SM, XX, XX</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||SM, XX, XX</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-20||2026-07-13||Examen 1||Examen||corregir_examen||Sección 1||JM, MB, NV</t>
+          <t>2026-07-20||2026-07-13||Examen 1||Examen||corregir_examen||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 3||EG, RM, XX</t>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 4||SM, XX, XX</t>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-27||2026-07-20||Examen 2||Examen||corregir_examen||Sección 1||JM, MB, NV</t>
+          <t>2026-07-27||2026-07-20||Examen 2||Examen||corregir_examen||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 3||EG, RM, XX</t>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 4||SM, XX, XX</t>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -5573,12 +5573,12 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5985,12 +5985,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>MB</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>RM</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>SM</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 1||JM, MB, NV</t>
+          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 1||JM, MB, NV</t>
+          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 3||EG, RM, XX</t>
+          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 3||EG, RM, XX</t>
+          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 4||SM, XX, XX</t>
+          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7255,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 4||SM, XX, XX</t>
+          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-05-08||2026-05-01||Día Nacional del Trabajo||Laboratorio||corregir_informe_laboratorio||Sección 3||EG, AR, XX, XX</t>
+          <t>2026-05-08||2026-05-01||Día Nacional del Trabajo||Laboratorio||corregir_informe_laboratorio||Sección 3||AR, JM, MB, EG</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-06-10||2026-06-03||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||JM, MB, NV</t>
+          <t>2026-06-10||2026-06-03||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 3||EG, RM, XX</t>
+          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 4||SM, XX, XX</t>
+          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-03||2026-06-26||Avance Laboratorio 2||Laboratorio||corregir_informe_laboratorio||Sección 3||EG, AR, XX, XX</t>
+          <t>2026-07-03||2026-06-26||Avance Laboratorio 2||Laboratorio||corregir_informe_laboratorio||Sección 3||AR, JM, MB, EG</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 1||JM, MB, NV</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 1||JM, MB, NV</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||EG, RM, XX</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||EG, RM, XX</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||EG, RM, XX</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||EG, RM, XX</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||SM, XX, XX</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||SM, XX, XX</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||SM, XX, XX</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||SM, XX, XX</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-06-29||2026-07-13||Examen 1||Examen||pedir_preguntas||Sección 1||JM, MB, NV</t>
+          <t>2026-06-29||2026-07-13||Examen 1||Examen||pedir_preguntas||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-20||2026-07-13||Examen 1||Examen||corregir_examen||Sección 1||JM, MB, NV</t>
+          <t>2026-07-20||2026-07-13||Examen 1||Examen||corregir_examen||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 3||EG, RM, XX</t>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 3||EG, RM, XX</t>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 4||SM, XX, XX</t>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 4||SM, XX, XX</t>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-06||2026-07-20||Examen 2||Examen||pedir_preguntas||Sección 1||JM, MB, NV</t>
+          <t>2026-07-06||2026-07-20||Examen 2||Examen||pedir_preguntas||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-27||2026-07-20||Examen 2||Examen||corregir_examen||Sección 1||JM, MB, NV</t>
+          <t>2026-07-27||2026-07-20||Examen 2||Examen||corregir_examen||Sección 1||JM, NV, MB</t>
         </is>
       </c>
     </row>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 3||EG, RM, XX</t>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 3||EG, RM, XX</t>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 3||JM, NV, EG</t>
         </is>
       </c>
     </row>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 4||SM, XX, XX</t>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 4||SM, XX, XX</t>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 4||RM, SM, XX</t>
         </is>
       </c>
     </row>

--- a/data/fokito/misiones.xlsx
+++ b/data/fokito/misiones.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 3||JM, NV, EG</t>
+          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 4||RM, SM, XX</t>
+          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 3||JM, NV, EG</t>
+          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 4||RM, SM, XX</t>
+          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-05-08||2026-05-01||Día Nacional del Trabajo||Laboratorio||corregir_informe_laboratorio||Sección 4||EG, SM, CC, XX</t>
+          <t>2026-05-08||2026-05-01||Día Nacional del Trabajo||Laboratorio||corregir_informe_laboratorio||Sección 4||EG, SM, CC, GF</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 3||JM, NV, EG</t>
+          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 4||RM, SM, XX</t>
+          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||JM, NV, EG</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||JM, NV, EG</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||RM, SM, XX</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||RM, SM, XX</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-06-29||2026-06-22||Avance Laboratorio 2||Laboratorio||corregir_informe_laboratorio||Sección 2||JCS, GM, VB, XX</t>
+          <t>2026-06-29||2026-06-22||Avance Laboratorio 2||Laboratorio||corregir_informe_laboratorio||Sección 2||JCS, GM, VB, EG</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 3||JM, NV, EG</t>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 4||RM, SM, XX</t>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-03||2026-06-26||Avance Laboratorio 2||Laboratorio||corregir_informe_laboratorio||Sección 4||EG, SM, CC, XX</t>
+          <t>2026-07-03||2026-06-26||Avance Laboratorio 2||Laboratorio||corregir_informe_laboratorio||Sección 4||EG, SM, CC, GF</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 3||JM, NV, EG</t>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 4||RM, SM, XX</t>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||JM, NV, EG</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||JM, NV, EG</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||RM, SM, XX</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||RM, SM, XX</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 3||JM, NV, EG</t>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 4||RM, SM, XX</t>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 3||JM, NV, EG</t>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 4||RM, SM, XX</t>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -5573,12 +5573,12 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
     </row>
@@ -5691,12 +5691,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -5775,12 +5775,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -5943,12 +5943,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>RM</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>GF</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 3||JM, NV, EG</t>
+          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 3||JM, NV, EG</t>
+          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 4||RM, SM, XX</t>
+          <t>2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7255,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 4||RM, SM, XX</t>
+          <t>2026-05-04||2026-04-27||Certamen 1||Certamen||corregir_y_notas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-05-08||2026-05-01||Día Nacional del Trabajo||Laboratorio||corregir_informe_laboratorio||Sección 4||EG, SM, CC, XX</t>
+          <t>2026-05-08||2026-05-01||Día Nacional del Trabajo||Laboratorio||corregir_informe_laboratorio||Sección 4||EG, SM, CC, GF</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 3||JM, NV, EG</t>
+          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 4||RM, SM, XX</t>
+          <t>2026-06-12||2026-06-05||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-06-29||2026-06-22||Avance Laboratorio 2||Laboratorio||corregir_informe_laboratorio||Sección 2||JCS, GM, VB, XX</t>
+          <t>2026-06-29||2026-06-22||Avance Laboratorio 2||Laboratorio||corregir_informe_laboratorio||Sección 2||JCS, GM, VB, EG</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-03||2026-06-26||Avance Laboratorio 2||Laboratorio||corregir_informe_laboratorio||Sección 4||EG, SM, CC, XX</t>
+          <t>2026-07-03||2026-06-26||Avance Laboratorio 2||Laboratorio||corregir_informe_laboratorio||Sección 4||EG, SM, CC, GF</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||JM, NV, EG</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||JM, NV, EG</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||JM, NV, EG</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||JM, NV, EG</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||RM, SM, XX</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||RM, SM, XX</t>
+          <t>2026-06-19||2026-07-03||Certamen 2||Certamen||pedir_preguntas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||RM, SM, XX</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||RM, SM, XX</t>
+          <t>2026-07-10||2026-07-03||Certamen 2||Certamen||corregir_y_notas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 3||JM, NV, EG</t>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 3||JM, NV, EG</t>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 4||RM, SM, XX</t>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 4||RM, SM, XX</t>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 3||JM, NV, EG</t>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 3||JM, NV, EG</t>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 3||JM, NV, RM</t>
         </is>
       </c>
     </row>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 4||RM, SM, XX</t>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 4||RM, SM, XX</t>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 4||EG, SM, GF</t>
         </is>
       </c>
     </row>

--- a/data/fokito/misiones.xlsx
+++ b/data/fokito/misiones.xlsx
@@ -127,52 +127,52 @@
     <t xml:space="preserve">SM</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-04-03||2026-03-27||Taller Unidad 1||Taller||corregir_taller||Sección 4||SM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certamen 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certamen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pedir_preguntas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JM, NV, MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enviar preguntas para certamen con solución. — Certamen 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 1||JM, NV, MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JM, NV, RM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 2||JM, NV, RM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 3||JM, NV, RM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EG, SM, GF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 4||EG, SM, GF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portafolio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revisar_portafolio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corregir portafolio del grupo de seminario. — Portafolio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pendiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-03||2026-03-27||Taller Unidad 1||Taller||corregir_taller||Sección 4||SM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certamen 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certamen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pedir_preguntas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JM, NV, MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enviar preguntas para certamen con solución. — Certamen 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 1||JM, NV, MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JM, NV, RM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 2||JM, NV, RM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 3||JM, NV, RM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EG, SM, GF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-13||2026-04-27||Certamen 1||Certamen||pedir_preguntas||Sección 4||EG, SM, GF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portafolio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">revisar_portafolio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corregir portafolio del grupo de seminario. — Portafolio</t>
   </si>
   <si>
     <t xml:space="preserve">2026-04-17||2026-04-10||Portafolio||Portafolio||revisar_portafolio||Sección 1||JM, NV, MB</t>
@@ -678,7 +678,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,12 +708,6 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -795,7 +789,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -817,10 +811,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1368,7 +1358,7 @@
       <c r="H6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -1400,7 +1390,7 @@
       <c r="H7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -1432,7 +1422,7 @@
       <c r="H8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J8" s="1" t="s">
@@ -1465,10 +1455,10 @@
         <v>26</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1479,28 +1469,28 @@
         <v>46139</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1511,28 +1501,28 @@
         <v>46139</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1543,28 +1533,28 @@
         <v>46139</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1575,28 +1565,28 @@
         <v>46139</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1607,25 +1597,25 @@
         <v>46122</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>48</v>
@@ -1639,25 +1629,25 @@
         <v>46122</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>48</v>
@@ -1671,25 +1661,25 @@
         <v>46122</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>49</v>
@@ -1703,25 +1693,25 @@
         <v>46122</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>49</v>
@@ -1735,25 +1725,25 @@
         <v>46122</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>50</v>
@@ -1767,25 +1757,25 @@
         <v>46122</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>50</v>
@@ -1799,25 +1789,25 @@
         <v>46122</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>51</v>
@@ -1831,25 +1821,25 @@
         <v>46122</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>51</v>
@@ -1863,10 +1853,10 @@
         <v>46139</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>52</v>
@@ -1881,7 +1871,7 @@
         <v>53</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>54</v>
@@ -1895,10 +1885,10 @@
         <v>46139</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>52</v>
@@ -1913,7 +1903,7 @@
         <v>53</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>56</v>
@@ -1927,10 +1917,10 @@
         <v>46139</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>52</v>
@@ -1945,7 +1935,7 @@
         <v>53</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>58</v>
@@ -1959,10 +1949,10 @@
         <v>46139</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>52</v>
@@ -1977,7 +1967,7 @@
         <v>53</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>60</v>
@@ -1991,10 +1981,10 @@
         <v>46139</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>61</v>
@@ -2009,7 +1999,7 @@
         <v>62</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>63</v>
@@ -2023,10 +2013,10 @@
         <v>46139</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>61</v>
@@ -2041,7 +2031,7 @@
         <v>62</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>64</v>
@@ -2055,10 +2045,10 @@
         <v>46139</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>61</v>
@@ -2073,7 +2063,7 @@
         <v>62</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>65</v>
@@ -2087,10 +2077,10 @@
         <v>46139</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>61</v>
@@ -2105,7 +2095,7 @@
         <v>62</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>66</v>
@@ -2119,10 +2109,10 @@
         <v>46139</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>67</v>
@@ -2131,13 +2121,13 @@
         <v>13</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>68</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>69</v>
@@ -2151,10 +2141,10 @@
         <v>46139</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>67</v>
@@ -2163,13 +2153,13 @@
         <v>18</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>68</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>70</v>
@@ -2201,7 +2191,7 @@
         <v>75</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>76</v>
@@ -2215,10 +2205,10 @@
         <v>46139</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>67</v>
@@ -2227,13 +2217,13 @@
         <v>20</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>68</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>77</v>
@@ -2247,10 +2237,10 @@
         <v>46139</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>67</v>
@@ -2259,13 +2249,13 @@
         <v>22</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>68</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>78</v>
@@ -2297,7 +2287,7 @@
         <v>75</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>80</v>
@@ -2329,7 +2319,7 @@
         <v>83</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>84</v>
@@ -2361,7 +2351,7 @@
         <v>87</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>88</v>
@@ -2393,7 +2383,7 @@
         <v>87</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>90</v>
@@ -2425,7 +2415,7 @@
         <v>83</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>91</v>
@@ -2457,7 +2447,7 @@
         <v>83</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>92</v>
@@ -2489,7 +2479,7 @@
         <v>83</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>94</v>
@@ -2503,25 +2493,25 @@
         <v>46150</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>95</v>
@@ -2535,25 +2525,25 @@
         <v>46150</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>96</v>
@@ -2567,25 +2557,25 @@
         <v>46150</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>97</v>
@@ -2599,25 +2589,25 @@
         <v>46150</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>98</v>
@@ -2649,7 +2639,7 @@
         <v>100</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>101</v>
@@ -2681,7 +2671,7 @@
         <v>100</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>102</v>
@@ -2713,7 +2703,7 @@
         <v>100</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>103</v>
@@ -2745,7 +2735,7 @@
         <v>100</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>105</v>
@@ -2771,13 +2761,13 @@
         <v>13</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>109</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>110</v>
@@ -2809,7 +2799,7 @@
         <v>112</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>113</v>
@@ -2823,25 +2813,25 @@
         <v>46178</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>114</v>
@@ -2855,25 +2845,25 @@
         <v>46178</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>115</v>
@@ -2899,13 +2889,13 @@
         <v>18</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>109</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>116</v>
@@ -2919,25 +2909,25 @@
         <v>46178</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>117</v>
@@ -2963,13 +2953,13 @@
         <v>20</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>109</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>118</v>
@@ -2983,25 +2973,25 @@
         <v>46178</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>119</v>
@@ -3027,13 +3017,13 @@
         <v>22</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>109</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>120</v>
@@ -3065,7 +3055,7 @@
         <v>112</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>121</v>
@@ -3097,7 +3087,7 @@
         <v>112</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>122</v>
@@ -3129,7 +3119,7 @@
         <v>112</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>123</v>
@@ -3146,22 +3136,22 @@
         <v>124</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>126</v>
@@ -3178,22 +3168,22 @@
         <v>124</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>127</v>
@@ -3210,22 +3200,22 @@
         <v>124</v>
       </c>
       <c r="D64" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>128</v>
@@ -3242,22 +3232,22 @@
         <v>124</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>129</v>
@@ -3289,7 +3279,7 @@
         <v>130</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>131</v>
@@ -3321,7 +3311,7 @@
         <v>130</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>132</v>
@@ -3353,7 +3343,7 @@
         <v>130</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>133</v>
@@ -3385,7 +3375,7 @@
         <v>130</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>134</v>
@@ -3402,7 +3392,7 @@
         <v>124</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>52</v>
@@ -3417,7 +3407,7 @@
         <v>135</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>136</v>
@@ -3434,7 +3424,7 @@
         <v>124</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>52</v>
@@ -3449,7 +3439,7 @@
         <v>135</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>137</v>
@@ -3466,7 +3456,7 @@
         <v>124</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>52</v>
@@ -3481,7 +3471,7 @@
         <v>135</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>138</v>
@@ -3498,7 +3488,7 @@
         <v>124</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>52</v>
@@ -3513,7 +3503,7 @@
         <v>135</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>139</v>
@@ -3545,7 +3535,7 @@
         <v>141</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>142</v>
@@ -3562,7 +3552,7 @@
         <v>124</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>61</v>
@@ -3577,7 +3567,7 @@
         <v>143</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>144</v>
@@ -3594,7 +3584,7 @@
         <v>124</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>61</v>
@@ -3609,7 +3599,7 @@
         <v>143</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>145</v>
@@ -3626,7 +3616,7 @@
         <v>124</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>61</v>
@@ -3641,7 +3631,7 @@
         <v>143</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>146</v>
@@ -3658,7 +3648,7 @@
         <v>124</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>61</v>
@@ -3673,7 +3663,7 @@
         <v>143</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>147</v>
@@ -3693,19 +3683,19 @@
         <v>149</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>151</v>
@@ -3725,19 +3715,19 @@
         <v>149</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>152</v>
@@ -3769,7 +3759,7 @@
         <v>141</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>153</v>
@@ -3789,19 +3779,19 @@
         <v>149</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>154</v>
@@ -3821,19 +3811,19 @@
         <v>149</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>155</v>
@@ -3865,7 +3855,7 @@
         <v>141</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>156</v>
@@ -3897,7 +3887,7 @@
         <v>157</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>158</v>
@@ -3929,7 +3919,7 @@
         <v>160</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>161</v>
@@ -3961,7 +3951,7 @@
         <v>160</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>162</v>
@@ -3981,19 +3971,19 @@
         <v>149</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>164</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>165</v>
@@ -4013,19 +4003,19 @@
         <v>149</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>164</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>166</v>
@@ -4057,7 +4047,7 @@
         <v>160</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>167</v>
@@ -4089,7 +4079,7 @@
         <v>160</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>168</v>
@@ -4109,19 +4099,19 @@
         <v>149</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>164</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>169</v>
@@ -4141,19 +4131,19 @@
         <v>149</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>164</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>170</v>
@@ -4185,7 +4175,7 @@
         <v>172</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>173</v>
@@ -4217,7 +4207,7 @@
         <v>172</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>174</v>
@@ -4234,7 +4224,7 @@
         <v>124</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>67</v>
@@ -4243,13 +4233,13 @@
         <v>13</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>175</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>176</v>
@@ -4266,7 +4256,7 @@
         <v>124</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>67</v>
@@ -4275,13 +4265,13 @@
         <v>18</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>175</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J97" s="1" t="s">
         <v>177</v>
@@ -4298,7 +4288,7 @@
         <v>124</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>67</v>
@@ -4307,13 +4297,13 @@
         <v>20</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>175</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>178</v>
@@ -4330,7 +4320,7 @@
         <v>124</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>67</v>
@@ -4339,13 +4329,13 @@
         <v>22</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>175</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>179</v>
@@ -4377,7 +4367,7 @@
         <v>172</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>180</v>
@@ -4409,7 +4399,7 @@
         <v>172</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J101" s="1" t="s">
         <v>181</v>
@@ -4441,7 +4431,7 @@
         <v>182</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>183</v>
@@ -4473,7 +4463,7 @@
         <v>182</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J103" s="1" t="s">
         <v>184</v>
@@ -4505,7 +4495,7 @@
         <v>182</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J104" s="1" t="s">
         <v>185</v>
@@ -4537,7 +4527,7 @@
         <v>182</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J105" s="1" t="s">
         <v>186</v>
@@ -4569,7 +4559,7 @@
         <v>187</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J106" s="1" t="s">
         <v>188</v>
@@ -4601,7 +4591,7 @@
         <v>187</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J107" s="1" t="s">
         <v>189</v>
@@ -4633,7 +4623,7 @@
         <v>187</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J108" s="1" t="s">
         <v>190</v>
@@ -4665,7 +4655,7 @@
         <v>187</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>191</v>
@@ -4691,13 +4681,13 @@
         <v>13</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>193</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J110" s="1" t="s">
         <v>194</v>
@@ -4723,13 +4713,13 @@
         <v>18</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>193</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J111" s="1" t="s">
         <v>195</v>
@@ -4755,13 +4745,13 @@
         <v>20</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>193</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J112" s="1" t="s">
         <v>196</v>
@@ -4787,13 +4777,13 @@
         <v>22</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>193</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J113" s="1" t="s">
         <v>197</v>
@@ -4819,13 +4809,13 @@
         <v>13</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J114" s="1" t="s">
         <v>199</v>
@@ -4851,13 +4841,13 @@
         <v>18</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J115" s="1" t="s">
         <v>200</v>
@@ -4883,13 +4873,13 @@
         <v>20</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J116" s="1" t="s">
         <v>201</v>
@@ -4915,13 +4905,13 @@
         <v>22</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J117" s="1" t="s">
         <v>202</v>
@@ -4958,28 +4948,28 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5045,10 +5035,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>52</v>
@@ -5071,10 +5061,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>67</v>
@@ -5083,24 +5073,24 @@
         <v>68</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>61</v>
@@ -5123,28 +5113,28 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5152,7 +5142,7 @@
         <v>124</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>52</v>
@@ -5178,7 +5168,7 @@
         <v>124</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>67</v>
@@ -5187,16 +5177,16 @@
         <v>175</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5204,7 +5194,7 @@
         <v>124</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>61</v>
@@ -5230,25 +5220,25 @@
         <v>124</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>125</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5311,16 +5301,16 @@
         <v>193</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5357,22 +5347,22 @@
         <v>149</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>150</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5415,16 +5405,16 @@
         <v>198</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5461,48 +5451,48 @@
         <v>149</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>164</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5675,16 +5665,16 @@
         <v>109</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -5712,13 +5702,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>209</v>
       </c>
     </row>
@@ -5887,34 +5877,34 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5944,7 +5934,7 @@
         <v>15</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>17</v>
@@ -5976,7 +5966,7 @@
         <v>26</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>27</v>
@@ -6008,7 +5998,7 @@
         <v>15</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>19</v>
@@ -6040,7 +6030,7 @@
         <v>26</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>29</v>
@@ -6072,7 +6062,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>21</v>
@@ -6104,7 +6094,7 @@
         <v>26</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>30</v>
@@ -6136,7 +6126,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>23</v>
@@ -6168,10 +6158,10 @@
         <v>26</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6182,25 +6172,25 @@
         <v>46122</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>48</v>
@@ -6214,25 +6204,25 @@
         <v>46122</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>48</v>
@@ -6246,25 +6236,25 @@
         <v>46122</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>49</v>
@@ -6278,25 +6268,25 @@
         <v>46122</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>49</v>
@@ -6310,25 +6300,25 @@
         <v>46122</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>50</v>
@@ -6342,25 +6332,25 @@
         <v>46122</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>50</v>
@@ -6374,25 +6364,25 @@
         <v>46122</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>51</v>
@@ -6406,25 +6396,25 @@
         <v>46122</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>51</v>
@@ -6438,28 +6428,28 @@
         <v>46139</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6470,10 +6460,10 @@
         <v>46139</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>52</v>
@@ -6488,7 +6478,7 @@
         <v>53</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>54</v>
@@ -6502,10 +6492,10 @@
         <v>46139</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>61</v>
@@ -6520,7 +6510,7 @@
         <v>62</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>63</v>
@@ -6534,10 +6524,10 @@
         <v>46139</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>67</v>
@@ -6546,13 +6536,13 @@
         <v>13</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>68</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>69</v>
@@ -6566,28 +6556,28 @@
         <v>46139</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6598,10 +6588,10 @@
         <v>46139</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>52</v>
@@ -6616,7 +6606,7 @@
         <v>53</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>56</v>
@@ -6630,10 +6620,10 @@
         <v>46139</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>61</v>
@@ -6648,7 +6638,7 @@
         <v>62</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>64</v>
@@ -6662,10 +6652,10 @@
         <v>46139</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>67</v>
@@ -6674,13 +6664,13 @@
         <v>18</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>68</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>70</v>
@@ -6712,7 +6702,7 @@
         <v>75</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>76</v>
@@ -6726,28 +6716,28 @@
         <v>46139</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6758,10 +6748,10 @@
         <v>46139</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>52</v>
@@ -6776,7 +6766,7 @@
         <v>53</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>58</v>
@@ -6790,10 +6780,10 @@
         <v>46139</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>61</v>
@@ -6808,7 +6798,7 @@
         <v>62</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>65</v>
@@ -6822,10 +6812,10 @@
         <v>46139</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>67</v>
@@ -6834,13 +6824,13 @@
         <v>20</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>68</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>77</v>
@@ -6854,28 +6844,28 @@
         <v>46139</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6886,10 +6876,10 @@
         <v>46139</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>52</v>
@@ -6904,7 +6894,7 @@
         <v>53</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>60</v>
@@ -6918,10 +6908,10 @@
         <v>46139</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>61</v>
@@ -6936,7 +6926,7 @@
         <v>62</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>66</v>
@@ -6950,10 +6940,10 @@
         <v>46139</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>67</v>
@@ -6962,13 +6952,13 @@
         <v>22</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>68</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>78</v>
@@ -7000,7 +6990,7 @@
         <v>75</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>80</v>
@@ -7032,7 +7022,7 @@
         <v>87</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>88</v>
@@ -7064,7 +7054,7 @@
         <v>87</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>90</v>
@@ -7078,25 +7068,25 @@
         <v>46150</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>95</v>
@@ -7110,25 +7100,25 @@
         <v>46150</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>96</v>
@@ -7142,25 +7132,25 @@
         <v>46150</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>97</v>
@@ -7174,25 +7164,25 @@
         <v>46150</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>98</v>
@@ -7224,7 +7214,7 @@
         <v>83</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>84</v>
@@ -7256,7 +7246,7 @@
         <v>100</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>101</v>
@@ -7288,7 +7278,7 @@
         <v>83</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>91</v>
@@ -7320,7 +7310,7 @@
         <v>100</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>102</v>
@@ -7352,7 +7342,7 @@
         <v>83</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>92</v>
@@ -7384,7 +7374,7 @@
         <v>100</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>103</v>
@@ -7416,7 +7406,7 @@
         <v>83</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>94</v>
@@ -7448,7 +7438,7 @@
         <v>100</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>105</v>
@@ -7474,13 +7464,13 @@
         <v>13</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>109</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>110</v>
@@ -7494,25 +7484,25 @@
         <v>46178</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>114</v>
@@ -7526,25 +7516,25 @@
         <v>46178</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>115</v>
@@ -7570,13 +7560,13 @@
         <v>18</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>109</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>116</v>
@@ -7590,25 +7580,25 @@
         <v>46178</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>117</v>
@@ -7634,13 +7624,13 @@
         <v>20</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>109</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>118</v>
@@ -7654,25 +7644,25 @@
         <v>46178</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>119</v>
@@ -7698,13 +7688,13 @@
         <v>22</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>109</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>120</v>
@@ -7736,7 +7726,7 @@
         <v>112</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>113</v>
@@ -7768,7 +7758,7 @@
         <v>130</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>131</v>
@@ -7800,7 +7790,7 @@
         <v>112</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>121</v>
@@ -7832,7 +7822,7 @@
         <v>130</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>132</v>
@@ -7864,7 +7854,7 @@
         <v>112</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>122</v>
@@ -7896,7 +7886,7 @@
         <v>130</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>133</v>
@@ -7928,7 +7918,7 @@
         <v>112</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>123</v>
@@ -7960,7 +7950,7 @@
         <v>130</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>134</v>
@@ -7992,7 +7982,7 @@
         <v>141</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>142</v>
@@ -8024,7 +8014,7 @@
         <v>141</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>153</v>
@@ -8056,7 +8046,7 @@
         <v>141</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>156</v>
@@ -8088,7 +8078,7 @@
         <v>157</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>158</v>
@@ -8105,22 +8095,22 @@
         <v>124</v>
       </c>
       <c r="D70" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>126</v>
@@ -8137,7 +8127,7 @@
         <v>124</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>52</v>
@@ -8152,7 +8142,7 @@
         <v>135</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>136</v>
@@ -8169,7 +8159,7 @@
         <v>124</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>61</v>
@@ -8184,7 +8174,7 @@
         <v>143</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>144</v>
@@ -8201,7 +8191,7 @@
         <v>124</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>67</v>
@@ -8210,13 +8200,13 @@
         <v>13</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>175</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>176</v>
@@ -8233,22 +8223,22 @@
         <v>124</v>
       </c>
       <c r="D74" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>127</v>
@@ -8265,7 +8255,7 @@
         <v>124</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>52</v>
@@ -8280,7 +8270,7 @@
         <v>135</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>137</v>
@@ -8297,7 +8287,7 @@
         <v>124</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>61</v>
@@ -8312,7 +8302,7 @@
         <v>143</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>145</v>
@@ -8329,7 +8319,7 @@
         <v>124</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>67</v>
@@ -8338,13 +8328,13 @@
         <v>18</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>175</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>177</v>
@@ -8361,22 +8351,22 @@
         <v>124</v>
       </c>
       <c r="D78" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>128</v>
@@ -8393,7 +8383,7 @@
         <v>124</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>52</v>
@@ -8408,7 +8398,7 @@
         <v>135</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>138</v>
@@ -8425,7 +8415,7 @@
         <v>124</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>61</v>
@@ -8440,7 +8430,7 @@
         <v>143</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>146</v>
@@ -8457,7 +8447,7 @@
         <v>124</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>67</v>
@@ -8466,13 +8456,13 @@
         <v>20</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>175</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>178</v>
@@ -8489,22 +8479,22 @@
         <v>124</v>
       </c>
       <c r="D82" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>129</v>
@@ -8521,7 +8511,7 @@
         <v>124</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>52</v>
@@ -8536,7 +8526,7 @@
         <v>135</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>139</v>
@@ -8553,7 +8543,7 @@
         <v>124</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>61</v>
@@ -8568,7 +8558,7 @@
         <v>143</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>147</v>
@@ -8585,7 +8575,7 @@
         <v>124</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>67</v>
@@ -8594,13 +8584,13 @@
         <v>22</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>175</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>179</v>
@@ -8620,19 +8610,19 @@
         <v>149</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>151</v>
@@ -8664,7 +8654,7 @@
         <v>160</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>161</v>
@@ -8696,7 +8686,7 @@
         <v>172</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>173</v>
@@ -8722,13 +8712,13 @@
         <v>13</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>193</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>194</v>
@@ -8748,19 +8738,19 @@
         <v>149</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>152</v>
@@ -8792,7 +8782,7 @@
         <v>160</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>162</v>
@@ -8824,7 +8814,7 @@
         <v>172</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>174</v>
@@ -8850,13 +8840,13 @@
         <v>18</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>193</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>195</v>
@@ -8876,19 +8866,19 @@
         <v>149</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>154</v>
@@ -8920,7 +8910,7 @@
         <v>160</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>167</v>
@@ -8952,7 +8942,7 @@
         <v>172</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>180</v>
@@ -8978,13 +8968,13 @@
         <v>20</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>193</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J97" s="1" t="s">
         <v>196</v>
@@ -9004,19 +8994,19 @@
         <v>149</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>155</v>
@@ -9048,7 +9038,7 @@
         <v>160</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>168</v>
@@ -9080,7 +9070,7 @@
         <v>172</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>181</v>
@@ -9106,13 +9096,13 @@
         <v>22</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>193</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J101" s="1" t="s">
         <v>197</v>
@@ -9132,19 +9122,19 @@
         <v>149</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>164</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>165</v>
@@ -9176,7 +9166,7 @@
         <v>182</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J103" s="1" t="s">
         <v>183</v>
@@ -9208,7 +9198,7 @@
         <v>187</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J104" s="1" t="s">
         <v>188</v>
@@ -9234,13 +9224,13 @@
         <v>13</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J105" s="1" t="s">
         <v>199</v>
@@ -9260,19 +9250,19 @@
         <v>149</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>164</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J106" s="1" t="s">
         <v>166</v>
@@ -9304,7 +9294,7 @@
         <v>182</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J107" s="1" t="s">
         <v>184</v>
@@ -9336,7 +9326,7 @@
         <v>187</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J108" s="1" t="s">
         <v>189</v>
@@ -9362,13 +9352,13 @@
         <v>18</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>200</v>
@@ -9388,19 +9378,19 @@
         <v>149</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>164</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J110" s="1" t="s">
         <v>169</v>
@@ -9432,7 +9422,7 @@
         <v>182</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J111" s="1" t="s">
         <v>185</v>
@@ -9464,7 +9454,7 @@
         <v>187</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J112" s="1" t="s">
         <v>190</v>
@@ -9490,13 +9480,13 @@
         <v>20</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J113" s="1" t="s">
         <v>201</v>
@@ -9516,19 +9506,19 @@
         <v>149</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>164</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J114" s="1" t="s">
         <v>170</v>
@@ -9560,7 +9550,7 @@
         <v>182</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J115" s="1" t="s">
         <v>186</v>
@@ -9592,7 +9582,7 @@
         <v>187</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J116" s="1" t="s">
         <v>191</v>
@@ -9618,13 +9608,13 @@
         <v>22</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J117" s="1" t="s">
         <v>202</v>
